--- a/api-catalog.xlsx
+++ b/api-catalog.xlsx
@@ -68,9 +68,6 @@
     <t>rest,internal</t>
   </si>
   <si>
-    <t>Finance</t>
-  </si>
-  <si>
     <t>my-soap-api</t>
   </si>
   <si>
@@ -83,9 +80,6 @@
     <t>soap,legacy</t>
   </si>
   <si>
-    <t>HR</t>
-  </si>
-  <si>
     <t>tags</t>
   </si>
   <si>
@@ -165,6 +159,12 @@
   </si>
   <si>
     <t>apis/soap/my-soap-api.wsdl</t>
+  </si>
+  <si>
+    <t>Finance: test1</t>
+  </si>
+  <si>
+    <t>HR: test2</t>
   </si>
 </sst>
 </file>
@@ -563,19 +563,19 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s">
         <v>6</v>
       </c>
       <c r="I1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" t="s">
         <v>21</v>
-      </c>
-      <c r="J1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -604,7 +604,7 @@
         <v>14</v>
       </c>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="K2" t="s">
         <v>8</v>
@@ -612,10 +612,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
         <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -624,22 +624,22 @@
         <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H3" t="s">
         <v>13</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="K3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -665,50 +665,50 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" t="s">
         <v>24</v>
       </c>
-      <c r="B1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>25</v>
-      </c>
-      <c r="D1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>29</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
         <v>33</v>
       </c>
-      <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -733,42 +733,42 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" t="s">
         <v>37</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>38</v>
       </c>
-      <c r="G1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" t="s">
-        <v>40</v>
-      </c>
       <c r="I1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -777,21 +777,21 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
@@ -800,13 +800,13 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" t="s">
         <v>42</v>
       </c>
-      <c r="G3" t="s">
-        <v>44</v>
-      </c>
       <c r="H3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/api-catalog.xlsx
+++ b/api-catalog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
   <si>
     <t>assetId</t>
   </si>
@@ -165,6 +165,12 @@
   </si>
   <si>
     <t>HR: test2</t>
+  </si>
+  <si>
+    <t>my-rest-api-2</t>
+  </si>
+  <si>
+    <t>my-soap-api-2</t>
   </si>
 </sst>
 </file>
@@ -580,7 +586,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -612,7 +618,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>

--- a/api-catalog.xlsx
+++ b/api-catalog.xlsx
@@ -167,10 +167,10 @@
     <t>HR: test2</t>
   </si>
   <si>
-    <t>my-rest-api-2</t>
-  </si>
-  <si>
-    <t>my-soap-api-2</t>
+    <t>my-rest-api-3</t>
+  </si>
+  <si>
+    <t>my-soap-api-3</t>
   </si>
 </sst>
 </file>

--- a/api-catalog.xlsx
+++ b/api-catalog.xlsx
@@ -167,10 +167,10 @@
     <t>HR: test2</t>
   </si>
   <si>
-    <t>my-rest-api-3</t>
-  </si>
-  <si>
-    <t>my-soap-api-3</t>
+    <t>my-rest-api-4</t>
+  </si>
+  <si>
+    <t>my-soap-api-4</t>
   </si>
 </sst>
 </file>

--- a/api-catalog.xlsx
+++ b/api-catalog.xlsx
@@ -167,10 +167,10 @@
     <t>HR: test2</t>
   </si>
   <si>
-    <t>my-rest-api-4</t>
-  </si>
-  <si>
-    <t>my-soap-api-4</t>
+    <t>my-rest-api-5</t>
+  </si>
+  <si>
+    <t>my-soap-api-5</t>
   </si>
 </sst>
 </file>

--- a/api-catalog.xlsx
+++ b/api-catalog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
   <si>
     <t>assetId</t>
   </si>
@@ -167,10 +167,16 @@
     <t>HR: test2</t>
   </si>
   <si>
-    <t>my-rest-api-5</t>
-  </si>
-  <si>
-    <t>my-soap-api-5</t>
+    <t>my-rest-api-6</t>
+  </si>
+  <si>
+    <t>my-soap-api-6</t>
+  </si>
+  <si>
+    <t>My REST API 6</t>
+  </si>
+  <si>
+    <t>My SOAP API 6</t>
   </si>
 </sst>
 </file>
@@ -589,7 +595,7 @@
         <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
@@ -621,7 +627,7 @@
         <v>49</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>

--- a/api-catalog.xlsx
+++ b/api-catalog.xlsx
@@ -167,16 +167,16 @@
     <t>HR: test2</t>
   </si>
   <si>
-    <t>my-rest-api-6</t>
-  </si>
-  <si>
-    <t>my-soap-api-6</t>
-  </si>
-  <si>
-    <t>My REST API 6</t>
-  </si>
-  <si>
-    <t>My SOAP API 6</t>
+    <t>my-rest-api-7</t>
+  </si>
+  <si>
+    <t>my-soap-api-7</t>
+  </si>
+  <si>
+    <t>My REST API 7</t>
+  </si>
+  <si>
+    <t>My SOAP API 7</t>
   </si>
 </sst>
 </file>

--- a/api-catalog.xlsx
+++ b/api-catalog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="55">
   <si>
     <t>assetId</t>
   </si>
@@ -167,16 +167,25 @@
     <t>HR: test2</t>
   </si>
   <si>
-    <t>my-rest-api-7</t>
-  </si>
-  <si>
-    <t>my-soap-api-7</t>
-  </si>
-  <si>
-    <t>My REST API 7</t>
-  </si>
-  <si>
-    <t>My SOAP API 7</t>
+    <t>clientId</t>
+  </si>
+  <si>
+    <t>test12345</t>
+  </si>
+  <si>
+    <t>test678910</t>
+  </si>
+  <si>
+    <t>my-rest-api-8</t>
+  </si>
+  <si>
+    <t>my-soap-api-8</t>
+  </si>
+  <si>
+    <t>My REST API 8</t>
+  </si>
+  <si>
+    <t>My SOAP API 8</t>
   </si>
 </sst>
 </file>
@@ -252,14 +261,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabella2" displayName="Tabella2" ref="A1:E3" totalsRowShown="0">
-  <autoFilter ref="A1:E3"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabella2" displayName="Tabella2" ref="A1:F3" totalsRowShown="0">
+  <autoFilter ref="A1:F3"/>
+  <tableColumns count="6">
     <tableColumn id="1" name="appName"/>
     <tableColumn id="2" name="description"/>
     <tableColumn id="3" name="url"/>
     <tableColumn id="4" name="redirectUri"/>
     <tableColumn id="5" name="grantTypes"/>
+    <tableColumn id="6" name="clientId"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -592,10 +602,10 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
@@ -624,10 +634,10 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -665,7 +675,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" customWidth="1"/>
@@ -675,7 +685,7 @@
     <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -691,8 +701,11 @@
       <c r="E1" t="s">
         <v>25</v>
       </c>
+      <c r="F1" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -708,8 +721,11 @@
       <c r="E2" t="s">
         <v>30</v>
       </c>
+      <c r="F2" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -721,6 +737,9 @@
       </c>
       <c r="E3" t="s">
         <v>30</v>
+      </c>
+      <c r="F3" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/api-catalog.xlsx
+++ b/api-catalog.xlsx
@@ -176,16 +176,16 @@
     <t>test678910</t>
   </si>
   <si>
-    <t>my-rest-api-8</t>
-  </si>
-  <si>
-    <t>my-soap-api-8</t>
-  </si>
-  <si>
-    <t>My REST API 8</t>
-  </si>
-  <si>
-    <t>My SOAP API 8</t>
+    <t>my-rest-api-9</t>
+  </si>
+  <si>
+    <t>my-soap-api-9</t>
+  </si>
+  <si>
+    <t>My REST API 9</t>
+  </si>
+  <si>
+    <t>My SOAP API 9</t>
   </si>
 </sst>
 </file>

--- a/api-catalog.xlsx
+++ b/api-catalog.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="APIs" sheetId="1" r:id="rId1"/>

--- a/api-catalog.xlsx
+++ b/api-catalog.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet name="APIs" sheetId="1" r:id="rId1"/>
     <sheet name="Applications" sheetId="2" r:id="rId2"/>
-    <sheet name="Contracts" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -21,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>assetId</t>
   </si>
@@ -44,9 +43,6 @@
     <t>imageFile</t>
   </si>
   <si>
-    <t>my-rest-api</t>
-  </si>
-  <si>
     <t>My REST API</t>
   </si>
   <si>
@@ -68,9 +64,6 @@
     <t>rest,internal</t>
   </si>
   <si>
-    <t>my-soap-api</t>
-  </si>
-  <si>
     <t>My SOAP API</t>
   </si>
   <si>
@@ -123,36 +116,6 @@
   </si>
   <si>
     <t>https://hrapp.example.com</t>
-  </si>
-  <si>
-    <t>groupId</t>
-  </si>
-  <si>
-    <t>versionGroup</t>
-  </si>
-  <si>
-    <t>apiId</t>
-  </si>
-  <si>
-    <t>tierId</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>{{orgId}}</t>
-  </si>
-  <si>
-    <t>{{apiId}}</t>
-  </si>
-  <si>
-    <t>APPROVED</t>
-  </si>
-  <si>
-    <t>{{tierId}}</t>
-  </si>
-  <si>
-    <t>customRuleset</t>
   </si>
   <si>
     <t>additionalFiles</t>
@@ -270,24 +233,6 @@
     <tableColumn id="4" name="redirectUri"/>
     <tableColumn id="5" name="grantTypes"/>
     <tableColumn id="6" name="clientId"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabella3" displayName="Tabella3" ref="A1:I3" totalsRowShown="0">
-  <autoFilter ref="A1:I3"/>
-  <tableColumns count="9">
-    <tableColumn id="1" name="appName"/>
-    <tableColumn id="2" name="assetId"/>
-    <tableColumn id="3" name="groupId"/>
-    <tableColumn id="4" name="version"/>
-    <tableColumn id="5" name="versionGroup"/>
-    <tableColumn id="6" name="apiId"/>
-    <tableColumn id="7" name="tierId"/>
-    <tableColumn id="8" name="status"/>
-    <tableColumn id="9" name="customRuleset"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -585,83 +530,83 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="H1" t="s">
         <v>6</v>
       </c>
       <c r="I1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" t="s">
         <v>19</v>
-      </c>
-      <c r="J1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>13</v>
       </c>
-      <c r="I2" t="s">
-        <v>14</v>
-      </c>
       <c r="J2" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="K2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J3" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="K3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -687,157 +632,59 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>23</v>
       </c>
-      <c r="D1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" t="s">
-        <v>25</v>
-      </c>
       <c r="F1" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
         <v>26</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>27</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>28</v>
       </c>
-      <c r="D2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" t="s">
-        <v>30</v>
-      </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
         <v>31</v>
       </c>
-      <c r="B3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" t="s">
-        <v>33</v>
-      </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="11.109375" customWidth="1"/>
-    <col min="3" max="3" width="9.5546875" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="14.21875" customWidth="1"/>
-    <col min="9" max="9" width="34.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H1" t="s">
         <v>38</v>
-      </c>
-      <c r="I1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/api-catalog.xlsx
+++ b/api-catalog.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
   </bookViews>
   <sheets>
     <sheet name="APIs" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
   <si>
     <t>assetId</t>
   </si>
@@ -149,6 +149,12 @@
   </si>
   <si>
     <t>My SOAP API 9</t>
+  </si>
+  <si>
+    <t>customRuleset</t>
+  </si>
+  <si>
+    <t>rulesets/axa-it-fundamentals.yaml</t>
   </si>
 </sst>
 </file>
@@ -204,9 +210,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabella1" displayName="Tabella1" ref="A1:K5" totalsRowShown="0">
-  <autoFilter ref="A1:K5"/>
-  <tableColumns count="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabella1" displayName="Tabella1" ref="A1:L5" totalsRowShown="0">
+  <autoFilter ref="A1:L5"/>
+  <tableColumns count="12">
     <tableColumn id="1" name="assetId"/>
     <tableColumn id="2" name="name"/>
     <tableColumn id="3" name="version"/>
@@ -218,6 +224,7 @@
     <tableColumn id="8" name="tags"/>
     <tableColumn id="9" name="categories"/>
     <tableColumn id="10" name="description"/>
+    <tableColumn id="12" name="customRuleset"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -501,16 +508,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="9" customWidth="1"/>
     <col min="4" max="4" width="11.77734375" customWidth="1"/>
     <col min="6" max="7" width="9.33203125" customWidth="1"/>
     <col min="8" max="8" width="10.77734375" customWidth="1"/>
+    <col min="12" max="12" width="29.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -544,8 +552,11 @@
       <c r="K1" t="s">
         <v>19</v>
       </c>
+      <c r="L1" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -576,8 +587,11 @@
       <c r="K2" t="s">
         <v>7</v>
       </c>
+      <c r="L2" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>40</v>
       </c>

--- a/api-catalog.xlsx
+++ b/api-catalog.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="APIs" sheetId="1" r:id="rId1"/>
     <sheet name="Applications" sheetId="2" r:id="rId2"/>
+    <sheet name="Certificates" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="56">
   <si>
     <t>assetId</t>
   </si>
@@ -155,13 +156,46 @@
   </si>
   <si>
     <t>rulesets/axa-it-fundamentals.yaml</t>
+  </si>
+  <si>
+    <t>certAlias</t>
+  </si>
+  <si>
+    <t>certFilePath</t>
+  </si>
+  <si>
+    <t>certFormat</t>
+  </si>
+  <si>
+    <t>certPassword</t>
+  </si>
+  <si>
+    <t>certSubjectDN</t>
+  </si>
+  <si>
+    <t>targetEnv</t>
+  </si>
+  <si>
+    <t>secretGroupName</t>
+  </si>
+  <si>
+    <t>truststoreName</t>
+  </si>
+  <si>
+    <t>useAsClientId</t>
+  </si>
+  <si>
+    <t>expirationDate</t>
+  </si>
+  <si>
+    <t>notes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,16 +203,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor theme="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -186,17 +234,77 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="1"/>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -240,6 +348,27 @@
     <tableColumn id="4" name="redirectUri"/>
     <tableColumn id="5" name="grantTypes"/>
     <tableColumn id="6" name="clientId"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabella3" displayName="Tabella3" ref="A1:L4" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+  <autoFilter ref="A1:L4"/>
+  <tableColumns count="12">
+    <tableColumn id="1" name="appName"/>
+    <tableColumn id="2" name="certAlias"/>
+    <tableColumn id="3" name="certFilePath"/>
+    <tableColumn id="4" name="certFormat"/>
+    <tableColumn id="5" name="certPassword"/>
+    <tableColumn id="6" name="certSubjectDN"/>
+    <tableColumn id="7" name="targetEnv"/>
+    <tableColumn id="8" name="secretGroupName"/>
+    <tableColumn id="9" name="truststoreName"/>
+    <tableColumn id="10" name="useAsClientId"/>
+    <tableColumn id="11" name="expirationDate"/>
+    <tableColumn id="12" name="notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -707,4 +836,70 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr defaultColWidth="29.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>